--- a/ecad-cost-profit-model.xlsx
+++ b/ecad-cost-profit-model.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="116">
   <si>
     <t xml:space="preserve">ECAD — Cost &amp; Profit Model</t>
   </si>
@@ -57,6 +57,24 @@
     <t xml:space="preserve">Mid-market rate, Aug 19 2026 — update periodically</t>
   </si>
   <si>
+    <t xml:space="preserve">JMMB POS monthly rental (JMD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official 2026 fee schedule — fixed cost regardless of job volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card transaction fee rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14% of transaction — only applies when client pays by card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs/month to cover POS rental (Tier 0 sedan baseline)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference only — most months this is covered well before mid-month</t>
+  </si>
+  <si>
     <t xml:space="preserve">Product Cost Per Car</t>
   </si>
   <si>
@@ -264,7 +282,16 @@
     <t xml:space="preserve">Margin %</t>
   </si>
   <si>
+    <t xml:space="preserve">Paid by Card?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit After Card Fee</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sedan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
   </si>
   <si>
     <t xml:space="preserve">SUV</t>
@@ -349,12 +376,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -535,7 +564,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -568,6 +597,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -580,7 +621,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -608,68 +649,40 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -924,7 +937,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D8"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -985,6 +998,40 @@
       </c>
       <c r="D8" s="7" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>4174.67</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <f aca="false">C10/2707</f>
+        <v>1.54217584041374</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1016,32 +1063,32 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>12</v>
+      <c r="B3" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>18</v>
+      <c r="B5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1049,20 +1096,20 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="13" t="n">
         <v>2500</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="15" t="n">
         <f aca="false">IFERROR(D6/E6,0)</f>
         <v>100</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1070,20 +1117,20 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="D7" s="13" t="n">
         <v>4108</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="16" t="n">
         <f aca="false">IFERROR(D7/E7,0)</f>
         <v>73.3571428571429</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1091,20 +1138,20 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" s="13" t="n">
         <v>3948</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">IFERROR(D8/E8,0)</f>
         <v>112.8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1112,20 +1159,20 @@
         <v>4</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" s="13" t="n">
         <v>5500</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="15" t="n">
         <f aca="false">IFERROR(D9/E9,0)</f>
         <v>85.9375</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1133,20 +1180,20 @@
         <v>5</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" s="13" t="n">
         <v>5500</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="14" t="n">
         <v>128</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">IFERROR(D10/E10,0)</f>
         <v>42.96875</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1154,20 +1201,20 @@
         <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" s="13" t="n">
         <v>5500</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="14" t="n">
         <v>128</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="15" t="n">
         <f aca="false">IFERROR(D11/E11,0)</f>
         <v>42.96875</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1175,20 +1222,20 @@
         <v>7</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="D12" s="13" t="n">
         <v>3111</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="18" t="n">
         <f aca="false">IFERROR(D12/E12,0)</f>
         <v>1244.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1196,20 +1243,20 @@
         <v>8</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="D13" s="13" t="n">
         <v>2354</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="16" t="n">
         <f aca="false">IFERROR(D13/E13,0)</f>
         <v>156.933333333333</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1217,20 +1264,20 @@
         <v>9</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="D14" s="13" t="n">
         <v>1838</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="16" t="n">
         <f aca="false">IFERROR(D14/E14,0)</f>
         <v>122.533333333333</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1238,20 +1285,20 @@
         <v>10</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="D15" s="13" t="n">
         <v>2520</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="16" t="n">
         <f aca="false">IFERROR(D15/E15,0)</f>
         <v>168</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1259,20 +1306,20 @@
         <v>11</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>2362</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="16" t="n">
         <f aca="false">IFERROR(D16/E16,0)</f>
         <v>157.466666666667</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1280,20 +1327,20 @@
         <v>12</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="D17" s="13" t="n">
         <v>2700</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">IFERROR(D17/E17,0)</f>
         <v>270</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1301,20 +1348,20 @@
         <v>13</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D18" s="13" t="n">
         <v>3000</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="16" t="n">
         <f aca="false">IFERROR(D18/E18,0)</f>
         <v>100</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1322,20 +1369,20 @@
         <v>14</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="D19" s="13" t="n">
         <v>1896</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="14" t="n">
         <v>12.5</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="16" t="n">
         <f aca="false">IFERROR(D19/E19,0)</f>
         <v>151.68</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1343,20 +1390,20 @@
         <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="13" t="n">
         <v>750</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="14" t="n">
         <v>6.5</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="16" t="n">
         <f aca="false">IFERROR(D20/E20,0)</f>
         <v>115.384615384615</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1364,20 +1411,20 @@
         <v>16</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D21" s="13" t="n">
         <v>1633</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="16" t="n">
         <f aca="false">IFERROR(D21/E21,0)</f>
         <v>163.3</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1385,20 +1432,20 @@
         <v>17</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="D22" s="13" t="n">
         <v>1264</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="16" t="n">
         <f aca="false">IFERROR(D22/E22,0)</f>
         <v>180.571428571429</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1406,20 +1453,20 @@
         <v>18</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="D23" s="13" t="n">
         <v>948</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="16" t="n">
         <f aca="false">IFERROR(D23/E23,0)</f>
         <v>94.8</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1427,20 +1474,20 @@
         <v>19</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="D24" s="13" t="n">
         <v>3790</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="16" t="n">
         <f aca="false">IFERROR(D24/E24,0)</f>
         <v>344.545454545455</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1448,20 +1495,20 @@
         <v>20</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="D25" s="13" t="n">
         <v>1300</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="16" t="n">
         <f aca="false">IFERROR(D25/E25,0)</f>
         <v>260</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1469,20 +1516,20 @@
         <v>21</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="D26" s="13" t="n">
         <v>2844</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="16" t="n">
         <f aca="false">IFERROR(D26/E26,0)</f>
         <v>177.75</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1490,20 +1537,20 @@
         <v>22</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="D27" s="13" t="n">
         <v>2844</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="14" t="n">
         <v>12.5</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="16" t="n">
         <f aca="false">IFERROR(D27/E27,0)</f>
         <v>227.52</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1511,56 +1558,56 @@
         <v>23</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="D28" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="16" t="n">
         <f aca="false">IFERROR(D28/E28,0)</f>
         <v>0</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16"/>
-      <c r="C30" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="10" t="n">
+      <c r="B30" s="19"/>
+      <c r="C30" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="13" t="n">
         <v>3626</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="14" t="n">
         <v>21.3</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="15" t="n">
         <f aca="false">IFERROR(D30/E30,0)</f>
         <v>170.234741784038</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16"/>
+      <c r="B31" s="19"/>
       <c r="C31" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="18" t="n">
+        <v>68</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="15" t="n">
         <f aca="false">F30/E31</f>
         <v>56.7449139280125</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1579,752 +1626,862 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F74"/>
+  <dimension ref="B2:H74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="24"/>
-      <c r="C6" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="26" t="n">
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="19"/>
+      <c r="C6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="25" t="n">
         <f aca="false">'Product Costs'!$F$6</f>
         <v>100</v>
       </c>
-      <c r="E6" s="24"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="24"/>
-      <c r="C7" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="26" t="n">
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="19"/>
+      <c r="C7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="25" t="n">
         <f aca="false">'Product Costs'!$F$17</f>
         <v>270</v>
       </c>
-      <c r="E7" s="24"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="24"/>
-      <c r="C8" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="26" t="n">
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="19"/>
+      <c r="C8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="25" t="n">
         <f aca="false">AVERAGE('Product Costs'!$F$23,'Product Costs'!$F$22)</f>
         <v>137.685714285714</v>
       </c>
-      <c r="E8" s="24"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="24"/>
-      <c r="C9" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="26" t="n">
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="19"/>
+      <c r="C9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="25" t="n">
         <f aca="false">'Product Costs'!$F$31</f>
         <v>56.7449139280125</v>
       </c>
-      <c r="E9" s="24"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="24"/>
-      <c r="C10" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="28" t="n">
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="19"/>
+      <c r="C10" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="17" t="n">
         <f aca="false">SUM(D6:D9)</f>
         <v>564.430628213727</v>
       </c>
-      <c r="E10" s="24"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="24"/>
-      <c r="C11" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="26" t="n">
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19"/>
+      <c r="C11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="25" t="n">
         <f aca="false">0.583*Assumptions!$C$6</f>
         <v>728.75</v>
       </c>
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="26" t="n">
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="19"/>
+      <c r="C12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="25" t="n">
         <f aca="false">Assumptions!$C$7</f>
         <v>1500</v>
       </c>
-      <c r="E12" s="24"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="24"/>
-      <c r="C13" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="29" t="n">
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="19"/>
+      <c r="C13" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="26" t="n">
         <f aca="false">D10+D11+D12</f>
         <v>2793.18062821373</v>
       </c>
-      <c r="E13" s="24"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C15" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>5500</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="15" t="n">
         <f aca="false">D16-D13</f>
         <v>2706.81937178627</v>
       </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="28" t="n">
         <f aca="false">IFERROR(E16/D16,0)</f>
         <v>0.492148976688413</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="30" t="n">
+      <c r="G16" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <f aca="false">IF(G16="Y",E16-(D16*Assumptions!$C$11),E16)</f>
+        <v>2706.81937178627</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>6500</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="15" t="n">
         <f aca="false">D17-D13</f>
         <v>3706.81937178627</v>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="28" t="n">
         <f aca="false">IFERROR(E17/D17,0)</f>
         <v>0.570279903351734</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="30" t="n">
+      <c r="G17" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <f aca="false">IF(G17="Y",E17-(D17*Assumptions!$C$11),E17)</f>
+        <v>3706.81937178627</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="6" t="n">
         <v>7500</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="15" t="n">
         <f aca="false">D18-D13</f>
         <v>4706.81937178627</v>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="28" t="n">
         <f aca="false">IFERROR(E18/D18,0)</f>
         <v>0.62757591623817</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="24"/>
-      <c r="C22" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="33" t="n">
+      <c r="G18" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <f aca="false">IF(G18="Y",E18-(D18*Assumptions!$C$11),E18)</f>
+        <v>4706.81937178627</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="19"/>
+      <c r="C22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="16" t="n">
         <f aca="false">'Tier Profitability'!$D$10</f>
         <v>564.430628213727</v>
       </c>
-      <c r="E22" s="24"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="24"/>
-      <c r="C23" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="26" t="n">
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="19"/>
+      <c r="C23" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="25" t="n">
         <f aca="false">'Product Costs'!$F$10</f>
         <v>42.96875</v>
       </c>
-      <c r="E23" s="24"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="24"/>
-      <c r="C24" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="26" t="n">
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="19"/>
+      <c r="C24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="25" t="n">
         <f aca="false">'Product Costs'!$F$8</f>
         <v>112.8</v>
       </c>
-      <c r="E24" s="24"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="24"/>
-      <c r="C25" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="26" t="n">
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="19"/>
+      <c r="C25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="25" t="n">
         <f aca="false">AVERAGE('Product Costs'!$F$23,'Product Costs'!$F$22)</f>
         <v>137.685714285714</v>
       </c>
-      <c r="E25" s="24"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="24"/>
-      <c r="C26" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="26" t="n">
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="19"/>
+      <c r="C26" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="25" t="n">
         <f aca="false">'Product Costs'!$F$19+'Product Costs'!$F$20</f>
         <v>267.064615384615</v>
       </c>
-      <c r="E26" s="24"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="24"/>
-      <c r="C27" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="26" t="n">
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="19"/>
+      <c r="C27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" s="25" t="n">
         <f aca="false">'Product Costs'!$F$24</f>
         <v>344.545454545455</v>
       </c>
-      <c r="E27" s="24"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="24"/>
-      <c r="C28" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="26" t="n">
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="19"/>
+      <c r="C28" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="25" t="n">
         <f aca="false">'Product Costs'!$F$17</f>
         <v>270</v>
       </c>
-      <c r="E28" s="24"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="24"/>
-      <c r="C29" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="28" t="n">
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="19"/>
+      <c r="C29" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="17" t="n">
         <f aca="false">SUM(D22:D28)</f>
         <v>1739.49516242951</v>
       </c>
-      <c r="E29" s="24"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="24"/>
-      <c r="C30" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="26" t="n">
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="19"/>
+      <c r="C30" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="25" t="n">
         <f aca="false">1.375*Assumptions!$C$6</f>
         <v>1718.75</v>
       </c>
-      <c r="E30" s="24"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="24"/>
-      <c r="C31" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="26" t="n">
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="19"/>
+      <c r="C31" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="25" t="n">
         <f aca="false">Assumptions!$C$7</f>
         <v>1500</v>
       </c>
-      <c r="E31" s="24"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="24"/>
-      <c r="C32" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="29" t="n">
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="19"/>
+      <c r="C32" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="26" t="n">
         <f aca="false">D29+D30+D31</f>
         <v>4958.24516242951</v>
       </c>
-      <c r="E32" s="24"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="19"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C34" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="6" t="n">
         <v>9000</v>
       </c>
-      <c r="E35" s="31" t="n">
+      <c r="E35" s="15" t="n">
         <f aca="false">D35-D32</f>
         <v>4041.75483757049</v>
       </c>
-      <c r="F35" s="32" t="n">
+      <c r="F35" s="28" t="n">
         <f aca="false">IFERROR(E35/D35,0)</f>
         <v>0.449083870841165</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="30" t="n">
+      <c r="G35" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <f aca="false">IF(G35="Y",E35-(D35*Assumptions!$C$11),E35)</f>
+        <v>4041.75483757049</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="6" t="n">
         <v>11000</v>
       </c>
-      <c r="E36" s="31" t="n">
+      <c r="E36" s="15" t="n">
         <f aca="false">D36-D32</f>
         <v>6041.75483757049</v>
       </c>
-      <c r="F36" s="32" t="n">
+      <c r="F36" s="28" t="n">
         <f aca="false">IFERROR(E36/D36,0)</f>
         <v>0.549250439779135</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="30" t="n">
+      <c r="G36" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <f aca="false">IF(G36="Y",E36-(D36*Assumptions!$C$11),E36)</f>
+        <v>6041.75483757049</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C37" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="6" t="n">
         <v>13000</v>
       </c>
-      <c r="E37" s="31" t="n">
+      <c r="E37" s="15" t="n">
         <f aca="false">D37-D32</f>
         <v>8041.75483757049</v>
       </c>
-      <c r="F37" s="32" t="n">
+      <c r="F37" s="28" t="n">
         <f aca="false">IFERROR(E37/D37,0)</f>
         <v>0.618596525966961</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="24"/>
-      <c r="C41" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D41" s="33" t="n">
+      <c r="G37" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <f aca="false">IF(G37="Y",E37-(D37*Assumptions!$C$11),E37)</f>
+        <v>8041.75483757049</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="19"/>
+      <c r="C41" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="16" t="n">
         <f aca="false">'Tier Profitability'!$D$29</f>
         <v>1739.49516242951</v>
       </c>
-      <c r="E41" s="24"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="24"/>
-      <c r="C42" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" s="26" t="n">
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="19"/>
+      <c r="C42" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="25" t="n">
         <f aca="false">'Product Costs'!$F$28</f>
         <v>0</v>
       </c>
-      <c r="E42" s="24"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="24"/>
-      <c r="C43" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="26" t="n">
+      <c r="E42" s="19"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="19"/>
+      <c r="C43" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="25" t="n">
         <f aca="false">'Product Costs'!$F$28</f>
         <v>0</v>
       </c>
-      <c r="E43" s="24"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="24"/>
-      <c r="C44" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="26" t="n">
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="19"/>
+      <c r="C44" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="25" t="n">
         <f aca="false">'Product Costs'!$F$26</f>
         <v>177.75</v>
       </c>
-      <c r="E44" s="24"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="24"/>
-      <c r="C45" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" s="26" t="n">
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="19"/>
+      <c r="C45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="25" t="n">
         <f aca="false">'Product Costs'!$F$14</f>
         <v>122.533333333333</v>
       </c>
-      <c r="E45" s="24"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="24"/>
-      <c r="C46" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D46" s="28" t="n">
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="19"/>
+      <c r="C46" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="17" t="n">
         <f aca="false">SUM(D41:D45)</f>
         <v>2039.77849576284</v>
       </c>
-      <c r="E46" s="24"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="24"/>
-      <c r="C47" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="26" t="n">
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="19"/>
+      <c r="C47" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" s="25" t="n">
         <f aca="false">2.5*Assumptions!$C$6</f>
         <v>3125</v>
       </c>
-      <c r="E47" s="24"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="24"/>
-      <c r="C48" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D48" s="26" t="n">
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="19"/>
+      <c r="C48" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" s="25" t="n">
         <f aca="false">Assumptions!$C$7</f>
         <v>1500</v>
       </c>
-      <c r="E48" s="24"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="24"/>
-      <c r="C49" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="29" t="n">
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="19"/>
+      <c r="C49" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="26" t="n">
         <f aca="false">D46+D47+D48</f>
         <v>6664.77849576285</v>
       </c>
-      <c r="E49" s="24"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E49" s="19"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C51" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="G51" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H51" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C52" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="6" t="n">
         <v>14500</v>
       </c>
-      <c r="E52" s="31" t="n">
+      <c r="E52" s="15" t="n">
         <f aca="false">D52-D49</f>
         <v>7835.22150423716</v>
       </c>
-      <c r="F52" s="32" t="n">
+      <c r="F52" s="28" t="n">
         <f aca="false">IFERROR(E52/D52,0)</f>
         <v>0.540360103740494</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="30" t="n">
+      <c r="G52" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H52" s="15" t="n">
+        <f aca="false">IF(G52="Y",E52-(D52*Assumptions!$C$11),E52)</f>
+        <v>7835.22150423716</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D53" s="6" t="n">
         <v>17500</v>
       </c>
-      <c r="E53" s="31" t="n">
+      <c r="E53" s="15" t="n">
         <f aca="false">D53-D49</f>
         <v>10835.2215042372</v>
       </c>
-      <c r="F53" s="32" t="n">
+      <c r="F53" s="28" t="n">
         <f aca="false">IFERROR(E53/D53,0)</f>
         <v>0.619155514527838</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D54" s="30" t="n">
+      <c r="G53" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <f aca="false">IF(G53="Y",E53-(D53*Assumptions!$C$11),E53)</f>
+        <v>10835.2215042372</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C54" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="6" t="n">
         <v>20500</v>
       </c>
-      <c r="E54" s="31" t="n">
+      <c r="E54" s="15" t="n">
         <f aca="false">D54-D49</f>
         <v>13835.2215042372</v>
       </c>
-      <c r="F54" s="32" t="n">
+      <c r="F54" s="28" t="n">
         <f aca="false">IFERROR(E54/D54,0)</f>
         <v>0.674888853865227</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="24"/>
-      <c r="C58" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" s="33" t="n">
+      <c r="G54" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <f aca="false">IF(G54="Y",E54-(D54*Assumptions!$C$11),E54)</f>
+        <v>13835.2215042372</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="19"/>
+      <c r="C58" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="16" t="n">
         <f aca="false">'Tier Profitability'!$D$46</f>
         <v>2039.77849576284</v>
       </c>
-      <c r="E58" s="24"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="24"/>
-      <c r="C59" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" s="26" t="n">
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="19"/>
+      <c r="C59" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" s="25" t="n">
         <f aca="false">'Product Costs'!$F$9</f>
         <v>85.9375</v>
       </c>
-      <c r="E59" s="24"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="24"/>
-      <c r="C60" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" s="26" t="n">
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="19"/>
+      <c r="C60" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D60" s="25" t="n">
         <f aca="false">'Product Costs'!$F$27</f>
         <v>227.52</v>
       </c>
-      <c r="E60" s="24"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="24"/>
-      <c r="C61" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D61" s="26" t="n">
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B61" s="19"/>
+      <c r="C61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="25" t="n">
         <f aca="false">'Product Costs'!$F$12</f>
         <v>1244.4</v>
       </c>
-      <c r="E61" s="24"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="24"/>
-      <c r="C62" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D62" s="26" t="n">
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="19"/>
+      <c r="C62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D62" s="25" t="n">
         <f aca="false">'Product Costs'!$F$13</f>
         <v>156.933333333333</v>
       </c>
-      <c r="E62" s="24"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="24"/>
-      <c r="C63" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D63" s="26" t="n">
+      <c r="E62" s="19"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B63" s="19"/>
+      <c r="C63" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="25" t="n">
         <f aca="false">'Product Costs'!$F$18</f>
         <v>100</v>
       </c>
-      <c r="E63" s="24"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="24"/>
-      <c r="C64" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64" s="26" t="n">
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B64" s="19"/>
+      <c r="C64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="25" t="n">
         <f aca="false">'Product Costs'!$F$15</f>
         <v>168</v>
       </c>
-      <c r="E64" s="24"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="24"/>
-      <c r="C65" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D65" s="26" t="n">
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B65" s="19"/>
+      <c r="C65" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" s="25" t="n">
         <f aca="false">'Product Costs'!$F$16</f>
         <v>157.466666666667</v>
       </c>
-      <c r="E65" s="24"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="24"/>
-      <c r="C66" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" s="28" t="n">
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="19"/>
+      <c r="C66" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" s="17" t="n">
         <f aca="false">SUM(D58:D65)</f>
         <v>4180.03599576284</v>
       </c>
-      <c r="E66" s="24"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="24"/>
-      <c r="C67" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D67" s="26" t="n">
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B67" s="19"/>
+      <c r="C67" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D67" s="25" t="n">
         <f aca="false">3.5*Assumptions!$C$6</f>
         <v>4375</v>
       </c>
-      <c r="E67" s="24"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="24"/>
-      <c r="C68" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" s="26" t="n">
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B68" s="19"/>
+      <c r="C68" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D68" s="25" t="n">
         <f aca="false">Assumptions!$C$7</f>
         <v>1500</v>
       </c>
-      <c r="E68" s="24"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="24"/>
-      <c r="C69" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" s="29" t="n">
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="19"/>
+      <c r="C69" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="26" t="n">
         <f aca="false">D66+D67+D68</f>
         <v>10055.0359957628</v>
       </c>
-      <c r="E69" s="24"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E69" s="19"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C71" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D72" s="30" t="n">
+        <v>85</v>
+      </c>
+      <c r="G71" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H71" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C72" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D72" s="6" t="n">
         <v>25500</v>
       </c>
-      <c r="E72" s="31" t="n">
+      <c r="E72" s="15" t="n">
         <f aca="false">D72-D69</f>
         <v>15444.9640042372</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F72" s="28" t="n">
         <f aca="false">IFERROR(E72/D72,0)</f>
         <v>0.605684862911261</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C73" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D73" s="30" t="n">
+      <c r="G72" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H72" s="15" t="n">
+        <f aca="false">IF(G72="Y",E72-(D72*Assumptions!$C$11),E72)</f>
+        <v>15444.9640042372</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C73" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D73" s="6" t="n">
         <v>31500</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E73" s="15" t="n">
         <f aca="false">D73-D69</f>
         <v>21444.9640042372</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F73" s="28" t="n">
         <f aca="false">IFERROR(E73/D73,0)</f>
         <v>0.680792508071021</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D74" s="30" t="n">
+      <c r="G73" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H73" s="15" t="n">
+        <f aca="false">IF(G73="Y",E73-(D73*Assumptions!$C$11),E73)</f>
+        <v>21444.9640042372</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C74" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="6" t="n">
         <v>37000</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E74" s="15" t="n">
         <f aca="false">D74-D69</f>
         <v>26944.9640042372</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F74" s="28" t="n">
         <f aca="false">IFERROR(E74/D74,0)</f>
         <v>0.728242270384788</v>
+      </c>
+      <c r="G74" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H74" s="15" t="n">
+        <f aca="false">IF(G74="Y",E74-(D74*Assumptions!$C$11),E74)</f>
+        <v>26944.9640042372</v>
       </c>
     </row>
   </sheetData>
